--- a/ZonasEscolares/excels/LIMA-LIMA-LA_MOLINA.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-LA_MOLINA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L43"/>
+  <dimension ref="A1:L46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2674,6 +2674,162 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>150114</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LA_MOLINA</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>307905</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>EL CASTILLO ENCANTADO</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>-12.06805</v>
+      </c>
+      <c r="H44" t="n">
+        <v>-76.95704000000001</v>
+      </c>
+      <c r="I44" t="n">
+        <v>64</v>
+      </c>
+      <c r="J44" t="n">
+        <v>6</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>150114</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LA_MOLINA</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>234301</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>LEARNING SCHOOL</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>-12.06803</v>
+      </c>
+      <c r="H45" t="n">
+        <v>-76.94408</v>
+      </c>
+      <c r="I45" t="n">
+        <v>115</v>
+      </c>
+      <c r="J45" t="n">
+        <v>16</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>150114</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LA_MOLINA</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>307665</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>SANTA MAGDALENA SOFIA BARAT</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>-12.06644</v>
+      </c>
+      <c r="H46" t="n">
+        <v>-76.9663</v>
+      </c>
+      <c r="I46" t="n">
+        <v>9</v>
+      </c>
+      <c r="J46" t="n">
+        <v>5</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ZonasEscolares/excels/LIMA-LIMA-LA_MOLINA.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-LA_MOLINA.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LA_MOLINA</t>
+          <t>LA MOLINA</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LA_MOLINA</t>
+          <t>LA MOLINA</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LA_MOLINA</t>
+          <t>LA MOLINA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LA_MOLINA</t>
+          <t>LA MOLINA</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -716,7 +716,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LA_MOLINA</t>
+          <t>LA MOLINA</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -768,7 +768,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LA_MOLINA</t>
+          <t>LA MOLINA</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LA_MOLINA</t>
+          <t>LA MOLINA</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LA_MOLINA</t>
+          <t>LA MOLINA</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LA_MOLINA</t>
+          <t>LA MOLINA</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LA_MOLINA</t>
+          <t>LA MOLINA</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LA_MOLINA</t>
+          <t>LA MOLINA</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LA_MOLINA</t>
+          <t>LA MOLINA</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LA_MOLINA</t>
+          <t>LA MOLINA</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LA_MOLINA</t>
+          <t>LA MOLINA</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LA_MOLINA</t>
+          <t>LA MOLINA</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LA_MOLINA</t>
+          <t>LA MOLINA</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LA_MOLINA</t>
+          <t>LA MOLINA</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LA_MOLINA</t>
+          <t>LA MOLINA</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LA_MOLINA</t>
+          <t>LA MOLINA</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LA_MOLINA</t>
+          <t>LA MOLINA</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LA_MOLINA</t>
+          <t>LA MOLINA</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1600,7 +1600,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LA_MOLINA</t>
+          <t>LA MOLINA</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LA_MOLINA</t>
+          <t>LA MOLINA</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LA_MOLINA</t>
+          <t>LA MOLINA</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LA_MOLINA</t>
+          <t>LA MOLINA</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LA_MOLINA</t>
+          <t>LA MOLINA</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LA_MOLINA</t>
+          <t>LA MOLINA</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LA_MOLINA</t>
+          <t>LA MOLINA</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LA_MOLINA</t>
+          <t>LA MOLINA</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1994,7 +1994,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LA_MOLINA</t>
+          <t>LA MOLINA</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2068,7 +2068,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LA_MOLINA</t>
+          <t>LA MOLINA</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LA_MOLINA</t>
+          <t>LA MOLINA</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2172,7 +2172,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LA_MOLINA</t>
+          <t>LA MOLINA</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LA_MOLINA</t>
+          <t>LA MOLINA</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2276,7 +2276,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LA_MOLINA</t>
+          <t>LA MOLINA</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2328,7 +2328,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LA_MOLINA</t>
+          <t>LA MOLINA</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LA_MOLINA</t>
+          <t>LA MOLINA</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LA_MOLINA</t>
+          <t>LA MOLINA</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LA_MOLINA</t>
+          <t>LA MOLINA</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LA_MOLINA</t>
+          <t>LA MOLINA</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2588,7 +2588,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LA_MOLINA</t>
+          <t>LA MOLINA</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LA_MOLINA</t>
+          <t>LA MOLINA</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LA_MOLINA</t>
+          <t>LA MOLINA</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LA_MOLINA</t>
+          <t>LA MOLINA</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LA_MOLINA</t>
+          <t>LA MOLINA</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/LIMA-LIMA-LA_MOLINA.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-LA_MOLINA.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>ATENEO DE LA MOLINA</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-12.10812</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-76.93940000000001</v>
-      </c>
-      <c r="I2" t="n">
-        <v>324</v>
-      </c>
-      <c r="J2" t="n">
-        <v>34</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-12.10812</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-76.9394</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>1286 HEROES DEL CENEPA</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-12.11708</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-76.93774999999999</v>
-      </c>
-      <c r="I3" t="n">
-        <v>641</v>
-      </c>
-      <c r="J3" t="n">
-        <v>30</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-12.11708</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-76.93775</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>641</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>1230 SULPICIO GARCIA PEÑALOZA</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-12.09547</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-76.94153</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1294</v>
-      </c>
-      <c r="J4" t="n">
-        <v>60</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-12.09547</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-76.94153</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1294</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>1235 UNION LATINOAMERICANA</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-12.06467</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-76.9426</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1728</v>
-      </c>
-      <c r="J5" t="n">
-        <v>69</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-12.06467</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-76.9426</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1728</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>140 VIRGEN DE LA MERCED</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-12.095732</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-76.94127899999999</v>
-      </c>
-      <c r="I6" t="n">
-        <v>297</v>
-      </c>
-      <c r="J6" t="n">
-        <v>14</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-12.095732</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-76.941279</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>297</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>1220 SAN JOSE MARELLO</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-12.0867</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-76.89061</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1505</v>
-      </c>
-      <c r="J7" t="n">
-        <v>61</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-12.0867</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-76.89061</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1505</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>136</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-12.06634</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-76.94078</v>
-      </c>
-      <c r="I8" t="n">
-        <v>487</v>
-      </c>
-      <c r="J8" t="n">
-        <v>26</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-12.06634</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-76.94078</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>487</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>1140 AURELIO MIRO QUESADA SOSA / 1140 AURELIO MIRO QUEZADA SOSA</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-12.08439</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-76.92801</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2058</v>
-      </c>
-      <c r="J9" t="n">
-        <v>92</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-12.08439</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-76.92801</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2058</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>0028 JESUS Y MARIA</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-12.07615</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-76.97365000000001</v>
-      </c>
-      <c r="I10" t="n">
-        <v>455</v>
-      </c>
-      <c r="J10" t="n">
-        <v>28</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-12.07615</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-76.97365</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>455</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>1278 MIXTO LA MOLINA</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-12.0704</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-76.94457</v>
-      </c>
-      <c r="I11" t="n">
-        <v>2502</v>
-      </c>
-      <c r="J11" t="n">
-        <v>73</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-12.0704</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-76.94457</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2502</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>FRANKLIN DELANO ROOSEVELT</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-12.07763</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-76.97153</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1145</v>
-      </c>
-      <c r="J12" t="n">
-        <v>155</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-12.07763</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-76.97153</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1145</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>ING. CARLOS LISSON BEINGOLEA</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-12.06741</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-76.95108</v>
-      </c>
-      <c r="I13" t="n">
-        <v>432</v>
-      </c>
-      <c r="J13" t="n">
-        <v>69</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-12.06741</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-76.95108</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>432</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>JEAN LE BOULCH</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-12.06473</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-76.94944</v>
-      </c>
-      <c r="I14" t="n">
-        <v>405</v>
-      </c>
-      <c r="J14" t="n">
-        <v>27</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-12.06473</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-76.94944</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>405</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>MAYOR PIP FELIX ROMAN TELLO ROJAS</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-12.07066</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-76.93974</v>
-      </c>
-      <c r="I15" t="n">
-        <v>876</v>
-      </c>
-      <c r="J15" t="n">
-        <v>44</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-12.07066</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-76.93974</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>876</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>SAGRADO CORAZON DE LA MOLINA</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-12.06417</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-76.95887999999999</v>
-      </c>
-      <c r="I16" t="n">
-        <v>387</v>
-      </c>
-      <c r="J16" t="n">
-        <v>31</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-12.06417</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-76.95888</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>387</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>ALTAIR</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-12.0934</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-76.95053</v>
-      </c>
-      <c r="I17" t="n">
-        <v>675</v>
-      </c>
-      <c r="J17" t="n">
-        <v>78</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-12.0934</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-76.95053</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>675</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>VILLA CARITAS</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-12.09922</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-76.92146</v>
-      </c>
-      <c r="I18" t="n">
-        <v>816</v>
-      </c>
-      <c r="J18" t="n">
-        <v>75</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-12.09922</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-76.92146</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>816</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>LORD BYRON</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-12.08319</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-76.90755</v>
-      </c>
-      <c r="I19" t="n">
-        <v>651</v>
-      </c>
-      <c r="J19" t="n">
-        <v>48</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-12.08319</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-76.90755</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>651</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1457,20 +1625,30 @@
           <t>COLEGIO PERUANO NORTEAMERICANO ABRAHAM LINCOLN</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-12.06776</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-76.96776</v>
-      </c>
-      <c r="I20" t="n">
-        <v>1343</v>
-      </c>
-      <c r="J20" t="n">
-        <v>185</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-12.06776</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-76.96776</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1343</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1509,20 +1687,30 @@
           <t>CLARIDAD</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-12.06368</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-76.94875</v>
-      </c>
-      <c r="I21" t="n">
-        <v>132</v>
-      </c>
-      <c r="J21" t="n">
-        <v>18</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-12.06368</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-76.94875</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1561,20 +1749,30 @@
           <t>SAINT PATRICK'S CHRISTIAN COLLEGE</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-12.07227</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-76.97020999999999</v>
-      </c>
-      <c r="I22" t="n">
-        <v>246</v>
-      </c>
-      <c r="J22" t="n">
-        <v>38</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-12.07227</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-76.97021</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1613,20 +1811,30 @@
           <t>JEAN PIAGET</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>-12.09906</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-76.94931</v>
-      </c>
-      <c r="I23" t="n">
-        <v>114</v>
-      </c>
-      <c r="J23" t="n">
-        <v>25</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-12.09906</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-76.94931</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1665,20 +1873,30 @@
           <t>HORMIGUITAS DE NEWMAN / JUAN ENRIQUE NEWMAN</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>-12.10236</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-76.94687999999999</v>
-      </c>
-      <c r="I24" t="n">
-        <v>453</v>
-      </c>
-      <c r="J24" t="n">
-        <v>32</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-12.10236</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-76.94688</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>453</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1717,20 +1935,30 @@
           <t>REINA DEL MUNDO</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>-12.09238</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-76.92596</v>
-      </c>
-      <c r="I25" t="n">
-        <v>908</v>
-      </c>
-      <c r="J25" t="n">
-        <v>75</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-12.09238</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-76.92596</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>908</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1769,20 +1997,30 @@
           <t>REINA DE LOS ANGELES</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>-12.07879</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-76.92567</v>
-      </c>
-      <c r="I26" t="n">
-        <v>495</v>
-      </c>
-      <c r="J26" t="n">
-        <v>61</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-12.07879</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-76.92567</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>495</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1821,20 +2059,30 @@
           <t>SAN VICENTE DE PAUL</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>-12.09807</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-76.94717</v>
-      </c>
-      <c r="I27" t="n">
-        <v>148</v>
-      </c>
-      <c r="J27" t="n">
-        <v>22</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-12.09807</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-76.94717</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1873,20 +2121,30 @@
           <t>SANTA CECILIA</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>-12.0639</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-76.9447</v>
-      </c>
-      <c r="I28" t="n">
-        <v>176</v>
-      </c>
-      <c r="J28" t="n">
-        <v>19</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-12.0639</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-76.9447</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1925,20 +2183,30 @@
           <t>SANTA FELICIA</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>-12.06312</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-76.95501</v>
-      </c>
-      <c r="I29" t="n">
-        <v>261</v>
-      </c>
-      <c r="J29" t="n">
-        <v>37</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-12.06312</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-76.95501</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1977,20 +2245,30 @@
           <t>NEWTON COLLEGE</t>
         </is>
       </c>
-      <c r="G30" t="n">
-        <v>-12.08138</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-76.92636</v>
-      </c>
-      <c r="I30" t="n">
-        <v>1218</v>
-      </c>
-      <c r="J30" t="n">
-        <v>192</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-12.08138</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-76.92636</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1218</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2029,20 +2307,30 @@
           <t>INMACULADO CORAZON DE MARIA</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>-12.08638</v>
-      </c>
-      <c r="H31" t="n">
-        <v>-76.88908000000001</v>
-      </c>
-      <c r="I31" t="n">
-        <v>228</v>
-      </c>
-      <c r="J31" t="n">
-        <v>12</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-12.08638</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-76.88908</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2081,20 +2369,30 @@
           <t>VILLA MARIA LA PLANICIE</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>-12.06875</v>
-      </c>
-      <c r="H32" t="n">
-        <v>-76.91048000000001</v>
-      </c>
-      <c r="I32" t="n">
-        <v>1139</v>
-      </c>
-      <c r="J32" t="n">
-        <v>116</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-12.06875</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-76.91048</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1139</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2133,20 +2431,30 @@
           <t>BRUNING</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>-12.06702</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-76.94618</v>
-      </c>
-      <c r="I33" t="n">
-        <v>120</v>
-      </c>
-      <c r="J33" t="n">
-        <v>26</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-12.06702</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-76.94618</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2185,20 +2493,30 @@
           <t>SAN PEDRO</t>
         </is>
       </c>
-      <c r="G34" t="n">
-        <v>-12.09914</v>
-      </c>
-      <c r="H34" t="n">
-        <v>-76.92149999999999</v>
-      </c>
-      <c r="I34" t="n">
-        <v>724</v>
-      </c>
-      <c r="J34" t="n">
-        <v>77</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-12.09914</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>-76.9215</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>724</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2237,20 +2555,30 @@
           <t>JACQUES COUSTEAU</t>
         </is>
       </c>
-      <c r="G35" t="n">
-        <v>-12.05755</v>
-      </c>
-      <c r="H35" t="n">
-        <v>-76.94486000000001</v>
-      </c>
-      <c r="I35" t="n">
-        <v>263</v>
-      </c>
-      <c r="J35" t="n">
-        <v>17</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-12.05755</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>-76.94486</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2289,20 +2617,30 @@
           <t>TRILCE DE LA MOLINA</t>
         </is>
       </c>
-      <c r="G36" t="n">
-        <v>-12.07258</v>
-      </c>
-      <c r="H36" t="n">
-        <v>-76.95798000000001</v>
-      </c>
-      <c r="I36" t="n">
-        <v>533</v>
-      </c>
-      <c r="J36" t="n">
-        <v>62</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-12.07258</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>-76.95798</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>533</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2341,20 +2679,30 @@
           <t>AUGUSTO SALAZAR BONDY</t>
         </is>
       </c>
-      <c r="G37" t="n">
-        <v>-12.10444</v>
-      </c>
-      <c r="H37" t="n">
-        <v>-76.94204000000001</v>
-      </c>
-      <c r="I37" t="n">
-        <v>219</v>
-      </c>
-      <c r="J37" t="n">
-        <v>4</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-12.10444</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>-76.94204</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2393,20 +2741,30 @@
           <t>PIRUETAS</t>
         </is>
       </c>
-      <c r="G38" t="n">
-        <v>-12.06276</v>
-      </c>
-      <c r="H38" t="n">
-        <v>-76.95259</v>
-      </c>
-      <c r="I38" t="n">
-        <v>26</v>
-      </c>
-      <c r="J38" t="n">
-        <v>4</v>
-      </c>
-      <c r="K38" t="n">
-        <v>1</v>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-12.06276</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>-76.95259</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2445,20 +2803,30 @@
           <t>CAPITAN FAP JOSE ABELARDO QUIÑONES</t>
         </is>
       </c>
-      <c r="G39" t="n">
-        <v>-12.06783</v>
-      </c>
-      <c r="H39" t="n">
-        <v>-76.97001</v>
-      </c>
-      <c r="I39" t="n">
-        <v>1226</v>
-      </c>
-      <c r="J39" t="n">
-        <v>111</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-12.06783</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>-76.97001</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1226</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2497,20 +2865,30 @@
           <t>NEW JEAN PIAGET COLLEGE</t>
         </is>
       </c>
-      <c r="G40" t="n">
-        <v>-12.11677</v>
-      </c>
-      <c r="H40" t="n">
-        <v>-76.93397</v>
-      </c>
-      <c r="I40" t="n">
-        <v>142</v>
-      </c>
-      <c r="J40" t="n">
-        <v>24</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-12.11677</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>-76.93397</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -2549,20 +2927,30 @@
           <t>HUMANITAS</t>
         </is>
       </c>
-      <c r="G41" t="n">
-        <v>-12.06757</v>
-      </c>
-      <c r="H41" t="n">
-        <v>-76.94738</v>
-      </c>
-      <c r="I41" t="n">
-        <v>162</v>
-      </c>
-      <c r="J41" t="n">
-        <v>14</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-12.06757</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>-76.94738</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2601,20 +2989,30 @@
           <t>SHALOOM</t>
         </is>
       </c>
-      <c r="G42" t="n">
-        <v>-12.08845</v>
-      </c>
-      <c r="H42" t="n">
-        <v>-76.88668</v>
-      </c>
-      <c r="I42" t="n">
-        <v>243</v>
-      </c>
-      <c r="J42" t="n">
-        <v>18</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-12.08845</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>-76.88668</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -2653,20 +3051,30 @@
           <t>DESCUBRIENDO</t>
         </is>
       </c>
-      <c r="G43" t="n">
-        <v>-12.08058</v>
-      </c>
-      <c r="H43" t="n">
-        <v>-76.93595999999999</v>
-      </c>
-      <c r="I43" t="n">
-        <v>226</v>
-      </c>
-      <c r="J43" t="n">
-        <v>9</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-12.08058</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>-76.93596</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -2705,20 +3113,30 @@
           <t>EL CASTILLO ENCANTADO</t>
         </is>
       </c>
-      <c r="G44" t="n">
-        <v>-12.06805</v>
-      </c>
-      <c r="H44" t="n">
-        <v>-76.95704000000001</v>
-      </c>
-      <c r="I44" t="n">
-        <v>64</v>
-      </c>
-      <c r="J44" t="n">
-        <v>6</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>-12.06805</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>-76.95704</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -2757,20 +3175,30 @@
           <t>LEARNING SCHOOL</t>
         </is>
       </c>
-      <c r="G45" t="n">
-        <v>-12.06803</v>
-      </c>
-      <c r="H45" t="n">
-        <v>-76.94408</v>
-      </c>
-      <c r="I45" t="n">
-        <v>115</v>
-      </c>
-      <c r="J45" t="n">
-        <v>16</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>-12.06803</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>-76.94408</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -2809,20 +3237,30 @@
           <t>SANTA MAGDALENA SOFIA BARAT</t>
         </is>
       </c>
-      <c r="G46" t="n">
-        <v>-12.06644</v>
-      </c>
-      <c r="H46" t="n">
-        <v>-76.9663</v>
-      </c>
-      <c r="I46" t="n">
-        <v>9</v>
-      </c>
-      <c r="J46" t="n">
-        <v>5</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-12.06644</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>-76.9663</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/LIMA-LIMA-LA_MOLINA.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-LA_MOLINA.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>164058</t>
+          <t>718271</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ATENEO DE LA MOLINA</t>
+          <t>CAPITAN FAP JOSE ABELARDO QUIÑONES</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-12.10812</t>
+          <t>-12.06783</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-76.9394</t>
+          <t>-76.97001</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>324</t>
+          <t>1226</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>111</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -536,7 +536,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -563,42 +563,42 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>307383</t>
+          <t>308245</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1286 HEROES DEL CENEPA</t>
+          <t>VILLA MARIA LA PLANICIE</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-12.11708</t>
+          <t>-12.06875</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-76.93775</t>
+          <t>-76.91048</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>641</t>
+          <t>1139</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>116</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>307401</t>
+          <t>308226</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1230 SULPICIO GARCIA PEÑALOZA</t>
+          <t>INMACULADO CORAZON DE MARIA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-12.09547</t>
+          <t>-12.08638</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-76.94153</t>
+          <t>-76.88908</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>228</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>307458</t>
+          <t>307463</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1235 UNION LATINOAMERICANA</t>
+          <t>140 VIRGEN DE LA MERCED</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-12.06467</t>
+          <t>-12.095732</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-76.9426</t>
+          <t>-76.941279</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1728</t>
+          <t>297</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -749,27 +749,27 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>307463</t>
+          <t>720472</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>140 VIRGEN DE LA MERCED</t>
+          <t>HUMANITAS</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-12.095732</t>
+          <t>-12.06757</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-76.941279</t>
+          <t>-76.94738</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>297</t>
+          <t>162</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>307477</t>
+          <t>307533</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1220 SAN JOSE MARELLO</t>
+          <t>FRANKLIN DELANO ROOSEVELT</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-12.0867</t>
+          <t>-12.07763</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-76.89061</t>
+          <t>-76.97153</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1505</t>
+          <t>1145</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>155</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>307482</t>
+          <t>234301</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>LEARNING SCHOOL</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-12.06634</t>
+          <t>-12.06803</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-76.94078</t>
+          <t>-76.94408</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>487</t>
+          <t>115</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>307496</t>
+          <t>308448</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1140 AURELIO MIRO QUESADA SOSA / 1140 AURELIO MIRO QUEZADA SOSA</t>
+          <t>JACQUES COUSTEAU</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-12.08439</t>
+          <t>-12.05755</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-76.92801</t>
+          <t>-76.94486</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2058</t>
+          <t>263</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>307514</t>
+          <t>307830</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0028 JESUS Y MARIA</t>
+          <t>CLARIDAD</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-12.07615</t>
+          <t>-12.06368</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-76.97365</t>
+          <t>-76.94875</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>132</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>307528</t>
+          <t>721396</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1278 MIXTO LA MOLINA</t>
+          <t>SHALOOM</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-12.0704</t>
+          <t>-12.08845</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-76.94457</t>
+          <t>-76.88668</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2502</t>
+          <t>243</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>307533</t>
+          <t>307811</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>FRANKLIN DELANO ROOSEVELT</t>
+          <t>COLEGIO PERUANO NORTEAMERICANO ABRAHAM LINCOLN</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-12.07763</t>
+          <t>-12.06776</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-76.97153</t>
+          <t>-76.96776</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1145</t>
+          <t>1343</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>185</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>307552</t>
+          <t>308151</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ING. CARLOS LISSON BEINGOLEA</t>
+          <t>SANTA CECILIA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-12.06741</t>
+          <t>-12.0639</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-76.95108</t>
+          <t>-76.9447</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>432</t>
+          <t>176</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>307571</t>
+          <t>308194</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>JEAN LE BOULCH</t>
+          <t>NEWTON COLLEGE</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-12.06473</t>
+          <t>-12.08138</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-76.94944</t>
+          <t>-76.92636</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>1218</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>192</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>307590</t>
+          <t>308146</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MAYOR PIP FELIX ROMAN TELLO ROJAS</t>
+          <t>SAN VICENTE DE PAUL</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-12.07066</t>
+          <t>-12.09807</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-76.93974</t>
+          <t>-76.94717</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>148</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>307689</t>
+          <t>718959</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>SAGRADO CORAZON DE LA MOLINA</t>
+          <t>NEW JEAN PIAGET COLLEGE</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-12.06417</t>
+          <t>-12.11677</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-76.95888</t>
+          <t>-76.93397</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>142</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>307694</t>
+          <t>307948</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ALTAIR</t>
+          <t>JEAN PIAGET</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-12.0934</t>
+          <t>-12.09906</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-76.95053</t>
+          <t>-76.94931</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>114</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>307707</t>
+          <t>307482</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>VILLA CARITAS</t>
+          <t>136</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-12.09922</t>
+          <t>-12.06634</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-76.92146</t>
+          <t>-76.94078</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>816</t>
+          <t>487</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>307793</t>
+          <t>308293</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>LORD BYRON</t>
+          <t>BRUNING</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-12.08319</t>
+          <t>-12.06702</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-76.90755</t>
+          <t>-76.94618</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>307811</t>
+          <t>307571</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>COLEGIO PERUANO NORTEAMERICANO ABRAHAM LINCOLN</t>
+          <t>JEAN LE BOULCH</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-12.06776</t>
+          <t>-12.06473</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-76.96776</t>
+          <t>-76.94944</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1343</t>
+          <t>405</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>307830</t>
+          <t>307514</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>CLARIDAD</t>
+          <t>0028 JESUS Y MARIA</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-12.06368</t>
+          <t>-12.07615</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-76.94875</t>
+          <t>-76.97365</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>455</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1741,42 +1741,42 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>307887</t>
+          <t>307383</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>SAINT PATRICK'S CHRISTIAN COLLEGE</t>
+          <t>1286 HEROES DEL CENEPA</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-12.07227</t>
+          <t>-12.11708</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-76.97021</t>
+          <t>-76.93775</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>641</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>307948</t>
+          <t>307689</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>JEAN PIAGET</t>
+          <t>SAGRADO CORAZON DE LA MOLINA</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-12.09906</t>
+          <t>-12.06417</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-76.94931</t>
+          <t>-76.95888</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>387</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>308108</t>
+          <t>164058</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>REINA DEL MUNDO</t>
+          <t>ATENEO DE LA MOLINA</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-12.09238</t>
+          <t>-12.10812</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-76.92596</t>
+          <t>-76.9394</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>908</t>
+          <t>324</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>308113</t>
+          <t>308170</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>REINA DE LOS ANGELES</t>
+          <t>SANTA FELICIA</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-12.07879</t>
+          <t>-12.06312</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-76.92567</t>
+          <t>-76.95501</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>261</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>308146</t>
+          <t>307887</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>SAN VICENTE DE PAUL</t>
+          <t>SAINT PATRICK'S CHRISTIAN COLLEGE</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-12.09807</t>
+          <t>-12.07227</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-76.94717</t>
+          <t>-76.97021</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>246</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>308151</t>
+          <t>308537</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>SANTA CECILIA</t>
+          <t>AUGUSTO SALAZAR BONDY</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-12.0639</t>
+          <t>-12.10444</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-76.9447</t>
+          <t>-76.94204</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>219</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2175,42 +2175,42 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>308170</t>
+          <t>605453</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>SANTA FELICIA</t>
+          <t>PIRUETAS</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-12.06312</t>
+          <t>-12.06276</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-76.95501</t>
+          <t>-76.95259</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>308194</t>
+          <t>307590</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>NEWTON COLLEGE</t>
+          <t>MAYOR PIP FELIX ROMAN TELLO ROJAS</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-12.08138</t>
+          <t>-12.07066</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-76.92636</t>
+          <t>-76.93974</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1218</t>
+          <t>876</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>308226</t>
+          <t>307793</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>INMACULADO CORAZON DE MARIA</t>
+          <t>LORD BYRON</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-12.08638</t>
+          <t>-12.08319</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-76.88908</t>
+          <t>-76.90755</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>651</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>48</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2334,7 +2334,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>308245</t>
+          <t>307665</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>VILLA MARIA LA PLANICIE</t>
+          <t>SANTA MAGDALENA SOFIA BARAT</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-12.06875</t>
+          <t>-12.06644</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-76.91048</t>
+          <t>-76.9663</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1139</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>308293</t>
+          <t>307905</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>BRUNING</t>
+          <t>EL CASTILLO ENCANTADO</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-12.06702</t>
+          <t>-12.06805</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-76.94618</t>
+          <t>-76.95704</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>64</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>308306</t>
+          <t>307401</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>SAN PEDRO</t>
+          <t>1230 SULPICIO GARCIA PEÑALOZA</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-12.09914</t>
+          <t>-12.09547</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-76.9215</t>
+          <t>-76.94153</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>724</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>60</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>308448</t>
+          <t>307477</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>JACQUES COUSTEAU</t>
+          <t>1220 SAN JOSE MARELLO</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-12.05755</t>
+          <t>-12.0867</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-76.94486</t>
+          <t>-76.89061</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>1505</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>61</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>308486</t>
+          <t>308113</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>TRILCE DE LA MOLINA</t>
+          <t>REINA DE LOS ANGELES</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-12.07258</t>
+          <t>-12.07879</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-76.95798</t>
+          <t>-76.92567</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>533</t>
+          <t>495</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>61</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>308537</t>
+          <t>308486</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>AUGUSTO SALAZAR BONDY</t>
+          <t>TRILCE DE LA MOLINA</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-12.10444</t>
+          <t>-12.07258</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-76.94204</t>
+          <t>-76.95798</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>533</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>62</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2733,42 +2733,42 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>605453</t>
+          <t>307458</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>PIRUETAS</t>
+          <t>1235 UNION LATINOAMERICANA</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-12.06276</t>
+          <t>-12.06467</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-76.95259</t>
+          <t>-76.9426</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>1728</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>69</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>718271</t>
+          <t>307552</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>CAPITAN FAP JOSE ABELARDO QUIÑONES</t>
+          <t>ING. CARLOS LISSON BEINGOLEA</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-12.06783</t>
+          <t>-12.06741</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-76.97001</t>
+          <t>-76.95108</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1226</t>
+          <t>432</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>69</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>718959</t>
+          <t>307528</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>NEW JEAN PIAGET COLLEGE</t>
+          <t>1278 MIXTO LA MOLINA</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-12.11677</t>
+          <t>-12.0704</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-76.93397</t>
+          <t>-76.94457</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>2502</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>73</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>720472</t>
+          <t>307707</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>HUMANITAS</t>
+          <t>VILLA CARITAS</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-12.06757</t>
+          <t>-12.09922</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-76.94738</t>
+          <t>-76.92146</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>816</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>75</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>721396</t>
+          <t>308108</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>SHALOOM</t>
+          <t>REINA DEL MUNDO</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-12.08845</t>
+          <t>-12.09238</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-76.88668</t>
+          <t>-76.92596</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>908</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>75</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3043,32 +3043,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>722051</t>
+          <t>308306</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>DESCUBRIENDO</t>
+          <t>SAN PEDRO</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-12.08058</t>
+          <t>-12.09914</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-76.93596</t>
+          <t>-76.9215</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>724</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>77</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3105,32 +3105,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>307905</t>
+          <t>307694</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>EL CASTILLO ENCANTADO</t>
+          <t>ALTAIR</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-12.06805</t>
+          <t>-12.0934</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-76.95704</t>
+          <t>-76.95053</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>675</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>78</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3167,32 +3167,32 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>234301</t>
+          <t>722051</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>LEARNING SCHOOL</t>
+          <t>DESCUBRIENDO</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-12.06803</t>
+          <t>-12.08058</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-76.94408</t>
+          <t>-76.93596</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>226</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3229,32 +3229,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>307665</t>
+          <t>307496</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>SANTA MAGDALENA SOFIA BARAT</t>
+          <t>1140 AURELIO MIRO QUESADA SOSA / 1140 AURELIO MIRO QUEZADA SOSA</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-12.06644</t>
+          <t>-12.08439</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-76.9663</t>
+          <t>-76.92801</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2058</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>92</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">

--- a/ZonasEscolares/excels/LIMA-LIMA-LA_MOLINA.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-LA_MOLINA.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>718271</t>
+          <t>722051</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CAPITAN FAP JOSE ABELARDO QUIÑONES</t>
+          <t>DESCUBRIENDO</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-12.06783</t>
+          <t>226</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-76.97001</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1226</t>
+          <t>-12.08058</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>-76.93596</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>308245</t>
+          <t>721396</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>VILLA MARIA LA PLANICIE</t>
+          <t>SHALOOM</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-12.06875</t>
+          <t>243</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-76.91048</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1139</t>
+          <t>-12.08845</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>-76.88668</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -598,7 +598,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>308226</t>
+          <t>720472</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>INMACULADO CORAZON DE MARIA</t>
+          <t>HUMANITAS</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-12.08638</t>
+          <t>162</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-76.88908</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>-12.06757</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-76.94738</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>307463</t>
+          <t>718959</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>140 VIRGEN DE LA MERCED</t>
+          <t>NEW JEAN PIAGET COLLEGE</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-12.095732</t>
+          <t>142</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-76.941279</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>297</t>
+          <t>-12.11677</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-76.93397</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>720472</t>
+          <t>718271</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>HUMANITAS</t>
+          <t>CAPITAN FAP JOSE ABELARDO QUIÑONES</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-12.06757</t>
+          <t>1226</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-76.94738</t>
+          <t>111</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>-12.06783</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-76.97001</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,37 +811,37 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>307533</t>
+          <t>605453</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>FRANKLIN DELANO ROOSEVELT</t>
+          <t>PIRUETAS</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-12.07763</t>
+          <t>26</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-76.97153</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1145</t>
+          <t>-12.06276</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>-76.95259</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>234301</t>
+          <t>308537</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>LEARNING SCHOOL</t>
+          <t>AUGUSTO SALAZAR BONDY</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-12.06803</t>
+          <t>219</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-76.94408</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>-12.10444</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-76.94204</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>308448</t>
+          <t>308486</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>JACQUES COUSTEAU</t>
+          <t>TRILCE DE LA MOLINA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-12.05755</t>
+          <t>533</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-76.94486</t>
+          <t>62</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>-12.07258</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-76.95798</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>307830</t>
+          <t>308448</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CLARIDAD</t>
+          <t>JACQUES COUSTEAU</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-12.06368</t>
+          <t>263</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-76.94875</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>-12.05755</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-76.94486</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>721396</t>
+          <t>308306</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SHALOOM</t>
+          <t>SAN PEDRO</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-12.08845</t>
+          <t>724</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-76.88668</t>
+          <t>77</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>-12.09914</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-76.9215</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>307811</t>
+          <t>308293</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>COLEGIO PERUANO NORTEAMERICANO ABRAHAM LINCOLN</t>
+          <t>BRUNING</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-12.06776</t>
+          <t>120</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-76.96776</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1343</t>
+          <t>-12.06702</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>-76.94618</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>308151</t>
+          <t>308245</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SANTA CECILIA</t>
+          <t>VILLA MARIA LA PLANICIE</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-12.0639</t>
+          <t>1139</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-76.9447</t>
+          <t>116</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>-12.06875</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-76.91048</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>308194</t>
+          <t>308226</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>NEWTON COLLEGE</t>
+          <t>INMACULADO CORAZON DE MARIA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-12.08138</t>
+          <t>228</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-76.92636</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1218</t>
+          <t>-12.08638</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>-76.88908</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>308146</t>
+          <t>308194</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>SAN VICENTE DE PAUL</t>
+          <t>NEWTON COLLEGE</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-12.09807</t>
+          <t>1218</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-76.94717</t>
+          <t>192</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>-12.08138</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-76.92636</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>718959</t>
+          <t>308170</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>NEW JEAN PIAGET COLLEGE</t>
+          <t>SANTA FELICIA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-12.11677</t>
+          <t>261</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-76.93397</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>-12.06312</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-76.95501</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>307948</t>
+          <t>308151</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>JEAN PIAGET</t>
+          <t>SANTA CECILIA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-12.09906</t>
+          <t>176</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-76.94931</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>-12.0639</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-76.9447</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>307482</t>
+          <t>308146</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>SAN VICENTE DE PAUL</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-12.06634</t>
+          <t>148</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-76.94078</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>487</t>
+          <t>-12.09807</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-76.94717</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>308293</t>
+          <t>308113</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>BRUNING</t>
+          <t>REINA DE LOS ANGELES</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-12.06702</t>
+          <t>495</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-76.94618</t>
+          <t>61</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>-12.07879</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-76.92567</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>307571</t>
+          <t>308108</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>JEAN LE BOULCH</t>
+          <t>REINA DEL MUNDO</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-12.06473</t>
+          <t>908</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-76.94944</t>
+          <t>75</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>-12.09238</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-76.92596</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>307514</t>
+          <t>307972</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0028 JESUS Y MARIA</t>
+          <t>HORMIGUITAS DE NEWMAN / JUAN ENRIQUE NEWMAN</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-12.07615</t>
+          <t>453</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-76.97365</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>-12.10236</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-76.94688</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,42 +1741,42 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>307383</t>
+          <t>307948</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1286 HEROES DEL CENEPA</t>
+          <t>JEAN PIAGET</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-12.11708</t>
+          <t>114</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-76.93775</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>641</t>
+          <t>-12.09906</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-76.94931</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>307689</t>
+          <t>307905</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>SAGRADO CORAZON DE LA MOLINA</t>
+          <t>EL CASTILLO ENCANTADO</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-12.06417</t>
+          <t>64</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-76.95888</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>-12.06805</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-76.95704</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>307972</t>
+          <t>307887</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>HORMIGUITAS DE NEWMAN / JUAN ENRIQUE NEWMAN</t>
+          <t>SAINT PATRICK'S CHRISTIAN COLLEGE</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-12.10236</t>
+          <t>246</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-76.94688</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>453</t>
+          <t>-12.07227</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>-76.97021</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>164058</t>
+          <t>307830</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ATENEO DE LA MOLINA</t>
+          <t>CLARIDAD</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-12.10812</t>
+          <t>132</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-76.9394</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>324</t>
+          <t>-12.06368</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>-76.94875</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>308170</t>
+          <t>307811</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>SANTA FELICIA</t>
+          <t>COLEGIO PERUANO NORTEAMERICANO ABRAHAM LINCOLN</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-12.06312</t>
+          <t>1343</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-76.95501</t>
+          <t>185</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>-12.06776</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>-76.96776</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>307887</t>
+          <t>307793</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>SAINT PATRICK'S CHRISTIAN COLLEGE</t>
+          <t>LORD BYRON</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-12.07227</t>
+          <t>651</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-76.97021</t>
+          <t>48</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>-12.08319</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>-76.90755</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>308537</t>
+          <t>307707</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>AUGUSTO SALAZAR BONDY</t>
+          <t>VILLA CARITAS</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-12.10444</t>
+          <t>816</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-76.94204</t>
+          <t>75</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>-12.09922</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-76.92146</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2175,42 +2175,42 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>605453</t>
+          <t>307694</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>PIRUETAS</t>
+          <t>ALTAIR</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-12.06276</t>
+          <t>675</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-76.95259</t>
+          <t>78</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-12.0934</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-76.95053</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>307590</t>
+          <t>307689</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>MAYOR PIP FELIX ROMAN TELLO ROJAS</t>
+          <t>SAGRADO CORAZON DE LA MOLINA</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-12.07066</t>
+          <t>387</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-76.93974</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>-12.06417</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>-76.95888</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>307793</t>
+          <t>307665</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>LORD BYRON</t>
+          <t>SANTA MAGDALENA SOFIA BARAT</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-12.08319</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-76.90755</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>-12.06644</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>-76.9663</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2334,7 +2334,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>307665</t>
+          <t>307590</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>SANTA MAGDALENA SOFIA BARAT</t>
+          <t>MAYOR PIP FELIX ROMAN TELLO ROJAS</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-12.06644</t>
+          <t>876</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-76.9663</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-12.07066</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>-76.93974</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>307905</t>
+          <t>307571</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>EL CASTILLO ENCANTADO</t>
+          <t>JEAN LE BOULCH</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-12.06805</t>
+          <t>405</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-76.95704</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>-12.06473</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>-76.94944</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>307401</t>
+          <t>307552</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1230 SULPICIO GARCIA PEÑALOZA</t>
+          <t>ING. CARLOS LISSON BEINGOLEA</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-12.09547</t>
+          <t>432</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-76.94153</t>
+          <t>69</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>-12.06741</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>-76.95108</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>307477</t>
+          <t>307533</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1220 SAN JOSE MARELLO</t>
+          <t>FRANKLIN DELANO ROOSEVELT</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-12.0867</t>
+          <t>1145</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-76.89061</t>
+          <t>155</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1505</t>
+          <t>-12.07763</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>-76.97153</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>308113</t>
+          <t>307528</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>REINA DE LOS ANGELES</t>
+          <t>1278 MIXTO LA MOLINA</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-12.07879</t>
+          <t>2502</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-76.92567</t>
+          <t>73</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>-12.0704</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>-76.94457</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>308486</t>
+          <t>307514</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>TRILCE DE LA MOLINA</t>
+          <t>0028 JESUS Y MARIA</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-12.07258</t>
+          <t>455</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-76.95798</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>533</t>
+          <t>-12.07615</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>-76.97365</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>307458</t>
+          <t>307496</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1235 UNION LATINOAMERICANA</t>
+          <t>1140 AURELIO MIRO QUESADA SOSA / 1140 AURELIO MIRO QUEZADA SOSA</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-12.06467</t>
+          <t>2058</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-76.9426</t>
+          <t>92</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1728</t>
+          <t>-12.08439</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>-76.92801</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>307552</t>
+          <t>307482</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>ING. CARLOS LISSON BEINGOLEA</t>
+          <t>136</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-12.06741</t>
+          <t>487</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-76.95108</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>432</t>
+          <t>-12.06634</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>-76.94078</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>307528</t>
+          <t>307477</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1278 MIXTO LA MOLINA</t>
+          <t>1220 SAN JOSE MARELLO</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-12.0704</t>
+          <t>1505</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-76.94457</t>
+          <t>61</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2502</t>
+          <t>-12.0867</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>-76.89061</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>307707</t>
+          <t>307463</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>VILLA CARITAS</t>
+          <t>140 VIRGEN DE LA MERCED</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-12.09922</t>
+          <t>297</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-76.92146</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>816</t>
+          <t>-12.095732</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>-76.941279</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>308108</t>
+          <t>307458</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>REINA DEL MUNDO</t>
+          <t>1235 UNION LATINOAMERICANA</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-12.09238</t>
+          <t>1728</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-76.92596</t>
+          <t>69</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>908</t>
+          <t>-12.06467</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>-76.9426</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3043,32 +3043,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>308306</t>
+          <t>307401</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>SAN PEDRO</t>
+          <t>1230 SULPICIO GARCIA PEÑALOZA</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-12.09914</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-76.9215</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>724</t>
+          <t>-12.09547</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>-76.94153</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3105,37 +3105,37 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>307694</t>
+          <t>307383</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>ALTAIR</t>
+          <t>1286 HEROES DEL CENEPA</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-12.0934</t>
+          <t>641</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-76.95053</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>-12.11708</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>-76.93775</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3167,32 +3167,32 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>722051</t>
+          <t>234301</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>DESCUBRIENDO</t>
+          <t>LEARNING SCHOOL</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-12.08058</t>
+          <t>115</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-76.93596</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>-12.06803</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-76.94408</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3229,32 +3229,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>307496</t>
+          <t>164058</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1140 AURELIO MIRO QUESADA SOSA / 1140 AURELIO MIRO QUEZADA SOSA</t>
+          <t>ATENEO DE LA MOLINA</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-12.08439</t>
+          <t>324</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-76.92801</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2058</t>
+          <t>-12.10812</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>-76.9394</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/LIMA-LIMA-LA_MOLINA.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-LA_MOLINA.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
